--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4210,6 +4210,472 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125472743</v>
+      </c>
+      <c r="B32" t="n">
+        <v>96729</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mickelsdamm , Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>338103</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6433693</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Tuvor med stor revmossa</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125472912</v>
+      </c>
+      <c r="B33" t="n">
+        <v>95705</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mickelsdamm , Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>338470</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6433751</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125472951</v>
+      </c>
+      <c r="B34" t="n">
+        <v>95705</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mickelsdamm , Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>338479</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6433734</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125474021</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8436</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mickelsdamm  Sopekärr , Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>338185</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6433735</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gångar på liggande björklåga vid Sopekärr</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -4215,7 +4215,7 @@
         <v>125472743</v>
       </c>
       <c r="B32" t="n">
-        <v>96729</v>
+        <v>96897</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125472912</v>
+        <v>125472951</v>
       </c>
       <c r="B33" t="n">
-        <v>95705</v>
+        <v>95873</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>338470</v>
+        <v>338479</v>
       </c>
       <c r="R33" t="n">
-        <v>6433751</v>
+        <v>6433734</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4445,10 +4445,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125472951</v>
+        <v>125472912</v>
       </c>
       <c r="B34" t="n">
-        <v>95705</v>
+        <v>95873</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>338479</v>
+        <v>338470</v>
       </c>
       <c r="R34" t="n">
-        <v>6433734</v>
+        <v>6433751</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -4212,10 +4212,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125472743</v>
+        <v>125474021</v>
       </c>
       <c r="B32" t="n">
-        <v>96897</v>
+        <v>8436</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4228,38 +4228,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mickelsdamm , Vg</t>
+          <t>Mickelsdamm  Sopekärr , Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>338103</v>
+        <v>338185</v>
       </c>
       <c r="R32" t="n">
-        <v>6433693</v>
+        <v>6433735</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4296,7 +4301,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Tuvor med stor revmossa</t>
+          <t>Gångar på liggande björklåga vid Sopekärr</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4308,11 +4313,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4329,10 +4329,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125472951</v>
+        <v>125472743</v>
       </c>
       <c r="B33" t="n">
-        <v>95873</v>
+        <v>96897</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4345,28 +4345,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -4377,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>338479</v>
+        <v>338103</v>
       </c>
       <c r="R33" t="n">
-        <v>6433734</v>
+        <v>6433693</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4413,6 +4409,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Tuvor med stor revmossa</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4445,7 +4446,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125472912</v>
+        <v>125472951</v>
       </c>
       <c r="B34" t="n">
         <v>95873</v>
@@ -4493,10 +4494,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>338470</v>
+        <v>338479</v>
       </c>
       <c r="R34" t="n">
-        <v>6433751</v>
+        <v>6433734</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4561,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125474021</v>
+        <v>125472912</v>
       </c>
       <c r="B35" t="n">
-        <v>8436</v>
+        <v>95873</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4577,43 +4578,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mickelsdamm  Sopekärr , Vg</t>
+          <t>Mickelsdamm , Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>338185</v>
+        <v>338470</v>
       </c>
       <c r="R35" t="n">
-        <v>6433735</v>
+        <v>6433751</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4648,11 +4648,6 @@
           <t>2025-05-23</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gångar på liggande björklåga vid Sopekärr</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4662,6 +4657,11 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -4327,7 +4327,7 @@
         <v>125472951</v>
       </c>
       <c r="B33" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>125472912</v>
       </c>
       <c r="B34" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>125472743</v>
       </c>
       <c r="B35" t="n">
-        <v>96952</v>
+        <v>96959</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -4327,7 +4327,7 @@
         <v>125472951</v>
       </c>
       <c r="B33" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>125472912</v>
       </c>
       <c r="B34" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>125472743</v>
       </c>
       <c r="B35" t="n">
-        <v>96959</v>
+        <v>96962</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -4327,7 +4327,7 @@
         <v>125472951</v>
       </c>
       <c r="B33" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>125472912</v>
       </c>
       <c r="B34" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>125472743</v>
       </c>
       <c r="B35" t="n">
-        <v>96962</v>
+        <v>96966</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -4327,7 +4327,7 @@
         <v>125472951</v>
       </c>
       <c r="B33" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>125472912</v>
       </c>
       <c r="B34" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>125472743</v>
       </c>
       <c r="B35" t="n">
-        <v>96966</v>
+        <v>96967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4656,6 +4656,349 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126193133</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97217</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>338449</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6433719</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>större yta ca 9 x 4 m. i sumpskog</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126193238</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>338459</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6433704</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126193156</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58508</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>338453</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6433720</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4327,7 +4327,7 @@
         <v>125472951</v>
       </c>
       <c r="B33" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>125472912</v>
       </c>
       <c r="B34" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>125472743</v>
       </c>
       <c r="B35" t="n">
-        <v>96967</v>
+        <v>96969</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>126193133</v>
       </c>
       <c r="B36" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>126193238</v>
       </c>
       <c r="B37" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>126193156</v>
       </c>
       <c r="B38" t="n">
-        <v>58508</v>
+        <v>58509</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4999,6 +4999,210 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126203036</v>
+      </c>
+      <c r="B39" t="n">
+        <v>95584</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>338481</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6433705</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126202928</v>
+      </c>
+      <c r="B40" t="n">
+        <v>95584</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>338449</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6433705</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -4661,7 +4661,7 @@
         <v>126193133</v>
       </c>
       <c r="B36" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>126203036</v>
       </c>
       <c r="B39" t="n">
-        <v>95584</v>
+        <v>95586</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>126202928</v>
       </c>
       <c r="B40" t="n">
-        <v>95584</v>
+        <v>95586</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4661,7 +4661,7 @@
         <v>126193133</v>
       </c>
       <c r="B36" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>126203036</v>
       </c>
       <c r="B39" t="n">
-        <v>95586</v>
+        <v>95588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>126202928</v>
       </c>
       <c r="B40" t="n">
-        <v>95586</v>
+        <v>95588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5203,6 +5203,218 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126280433</v>
+      </c>
+      <c r="B41" t="n">
+        <v>95948</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>338406</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6433747</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126280430</v>
+      </c>
+      <c r="B42" t="n">
+        <v>95948</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>338322</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6433729</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -4661,7 +4661,7 @@
         <v>126193133</v>
       </c>
       <c r="B36" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>126193238</v>
       </c>
       <c r="B37" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>126193156</v>
       </c>
       <c r="B38" t="n">
-        <v>58509</v>
+        <v>58513</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>126203036</v>
       </c>
       <c r="B39" t="n">
-        <v>95588</v>
+        <v>95592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>126202928</v>
       </c>
       <c r="B40" t="n">
-        <v>95588</v>
+        <v>95592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>126280433</v>
       </c>
       <c r="B41" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126280430</v>
       </c>
       <c r="B42" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4661,7 +4661,7 @@
         <v>126193133</v>
       </c>
       <c r="B36" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>126203036</v>
       </c>
       <c r="B39" t="n">
-        <v>95592</v>
+        <v>95595</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>126202928</v>
       </c>
       <c r="B40" t="n">
-        <v>95592</v>
+        <v>95595</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>126280433</v>
       </c>
       <c r="B41" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126280430</v>
       </c>
       <c r="B42" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5415,6 +5415,115 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126391656</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58297</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>337674</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6433658</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5524,6 +5524,658 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126398365</v>
+      </c>
+      <c r="B44" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>338008</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6433676</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ca 45 - 50 cm hög i äldre skog</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126398382</v>
+      </c>
+      <c r="B45" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>338036</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6433654</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126398378</v>
+      </c>
+      <c r="B46" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>337846</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6433661</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ca 45 - 50 cm hög i äldre skog</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126398359</v>
+      </c>
+      <c r="B47" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>338012</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6433665</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ca 45 - 50 cm hög i äldre skog</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126398385</v>
+      </c>
+      <c r="B48" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>338031</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6433661</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126398373</v>
+      </c>
+      <c r="B49" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>337826</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6433635</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Blåmossa växer ihop och täcker en större yta ca 3 x 2 m</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6176,6 +6176,459 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126475340</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>338007</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6433672</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På hällmark i äldre tall / barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126475328</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>338009</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6433681</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126475807</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>337732</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6433633</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska hackspår i barrlåga</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126475899</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58027</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>338013</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6433667</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4661,7 +4661,7 @@
         <v>126193133</v>
       </c>
       <c r="B36" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>126193238</v>
       </c>
       <c r="B37" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>126193156</v>
       </c>
       <c r="B38" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>126203036</v>
       </c>
       <c r="B39" t="n">
-        <v>95595</v>
+        <v>95604</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>126202928</v>
       </c>
       <c r="B40" t="n">
-        <v>95595</v>
+        <v>95604</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>126280433</v>
       </c>
       <c r="B41" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126280430</v>
       </c>
       <c r="B42" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>126391656</v>
       </c>
       <c r="B43" t="n">
-        <v>58297</v>
+        <v>58300</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>126398365</v>
       </c>
       <c r="B44" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>126398382</v>
       </c>
       <c r="B45" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>126398378</v>
       </c>
       <c r="B46" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>126398359</v>
       </c>
       <c r="B47" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>126398385</v>
       </c>
       <c r="B48" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>126398373</v>
       </c>
       <c r="B49" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126475807</v>
+        <v>126476117</v>
       </c>
       <c r="B52" t="n">
         <v>57654</v>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>337732</v>
+        <v>338031</v>
       </c>
       <c r="R52" t="n">
-        <v>6433633</v>
+        <v>6433671</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6481,17 +6481,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska hackspår i barrlåga</t>
+          <t>Färska hack i barrlåga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6518,10 +6518,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126475899</v>
+        <v>126476075</v>
       </c>
       <c r="B53" t="n">
-        <v>58027</v>
+        <v>58516</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6529,21 +6529,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>208249</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6551,17 +6551,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6569,13 +6566,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>338013</v>
+        <v>337974</v>
       </c>
       <c r="R53" t="n">
-        <v>6433667</v>
+        <v>6433674</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6599,12 +6596,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6613,6 +6610,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6628,6 +6626,229 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126475807</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>337732</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6433633</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska hackspår i barrlåga</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126475899</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58027</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>338013</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6433667</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6850,6 +6850,154 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129357810</v>
+      </c>
+      <c r="B56" t="n">
+        <v>56593</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår Sopekärr , Vg</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>338168</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6433691</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Flertalet ljudupptagningar i sumpskog med kärräng. Hålträn finns i området, upplever området som en passande miljö för arten.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Sumpskog med kärräng, blandskog</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6998,6 +6998,139 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129529866</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56593</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>338096</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6433664</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -6855,7 +6855,7 @@
         <v>129357810</v>
       </c>
       <c r="B56" t="n">
-        <v>56593</v>
+        <v>56596</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>129529866</v>
       </c>
       <c r="B57" t="n">
-        <v>56593</v>
+        <v>56596</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -6855,7 +6855,7 @@
         <v>129357810</v>
       </c>
       <c r="B56" t="n">
-        <v>56596</v>
+        <v>56601</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>129529866</v>
       </c>
       <c r="B57" t="n">
-        <v>56596</v>
+        <v>56601</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -6855,7 +6855,7 @@
         <v>129357810</v>
       </c>
       <c r="B56" t="n">
-        <v>56601</v>
+        <v>56602</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>129529866</v>
       </c>
       <c r="B57" t="n">
-        <v>56601</v>
+        <v>56602</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7131,6 +7131,154 @@
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129914481</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56602</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Sopekärr , Vg</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>338168</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6433692</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>28-30 kHz</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Naturskog, kuperad blandskog med våtmark och öppna luckor</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -7136,7 +7136,7 @@
         <v>129914481</v>
       </c>
       <c r="B58" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -7136,7 +7136,7 @@
         <v>129914481</v>
       </c>
       <c r="B58" t="n">
-        <v>56606</v>
+        <v>56691</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -7136,7 +7136,7 @@
         <v>129914481</v>
       </c>
       <c r="B58" t="n">
-        <v>56691</v>
+        <v>56606</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 22640-2025 artfynd.xlsx
+++ b/artfynd/A 22640-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4212,10 +4212,15 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125474021</v>
+        <v>121349455</v>
       </c>
       <c r="B32" t="n">
-        <v>8436</v>
+        <v>97061</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4223,46 +4228,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>221944</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mickelsdamm  Sopekärr , Vg</t>
+          <t>Ale-Mickelsdamm/Intakan, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>338185</v>
+        <v>337917</v>
       </c>
       <c r="R32" t="n">
-        <v>6433735</v>
+        <v>6433695</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4286,17 +4286,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gångar på liggande björklåga vid Sopekärr</t>
+          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4312,22 +4312,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125472951</v>
+        <v>121349471</v>
       </c>
       <c r="B33" t="n">
-        <v>95944</v>
+        <v>97061</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4335,26 +4340,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>221944</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4363,17 +4364,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mickelsdamm , Vg</t>
+          <t>Ale-Mickelsdamm/Intakan, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>338479</v>
+        <v>337968</v>
       </c>
       <c r="R33" t="n">
-        <v>6433734</v>
+        <v>6433680</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4397,12 +4398,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4415,30 +4421,25 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125472912</v>
+        <v>125474021</v>
       </c>
       <c r="B34" t="n">
-        <v>95944</v>
+        <v>8436</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4446,42 +4447,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mickelsdamm , Vg</t>
+          <t>Mickelsdamm  Sopekärr , Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>338470</v>
+        <v>338185</v>
       </c>
       <c r="R34" t="n">
-        <v>6433751</v>
+        <v>6433735</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4516,6 +4518,11 @@
           <t>2025-05-23</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gångar på liggande björklåga vid Sopekärr</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4525,11 +4532,6 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4546,10 +4548,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125472743</v>
+        <v>125472951</v>
       </c>
       <c r="B35" t="n">
-        <v>96969</v>
+        <v>95944</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4557,24 +4559,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -4585,10 +4591,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>338103</v>
+        <v>338479</v>
       </c>
       <c r="R35" t="n">
-        <v>6433693</v>
+        <v>6433734</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4621,11 +4627,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Tuvor med stor revmossa</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4658,10 +4659,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126193133</v>
+        <v>125472912</v>
       </c>
       <c r="B36" t="n">
-        <v>97239</v>
+        <v>95944</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4669,38 +4670,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Mickelsdamm , Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>338449</v>
+        <v>338470</v>
       </c>
       <c r="R36" t="n">
-        <v>6433719</v>
+        <v>6433751</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4727,17 +4732,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>större yta ca 9 x 4 m. i sumpskog</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4753,11 +4753,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4775,10 +4770,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126193238</v>
+        <v>125472743</v>
       </c>
       <c r="B37" t="n">
-        <v>58027</v>
+        <v>96969</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4786,46 +4781,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Mickelsdamm , Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>338459</v>
+        <v>338103</v>
       </c>
       <c r="R37" t="n">
-        <v>6433704</v>
+        <v>6433693</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4852,12 +4839,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Tuvor med stor revmossa</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4866,8 +4858,14 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4884,10 +4882,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126193156</v>
+        <v>126193133</v>
       </c>
       <c r="B38" t="n">
-        <v>58516</v>
+        <v>97239</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4895,32 +4893,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4928,10 +4921,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>338453</v>
+        <v>338449</v>
       </c>
       <c r="R38" t="n">
-        <v>6433720</v>
+        <v>6433719</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4964,6 +4957,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>större yta ca 9 x 4 m. i sumpskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5001,10 +4999,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126203036</v>
+        <v>126193238</v>
       </c>
       <c r="B39" t="n">
-        <v>95604</v>
+        <v>58027</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5012,27 +5010,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5040,10 +5046,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>338481</v>
+        <v>338459</v>
       </c>
       <c r="R39" t="n">
-        <v>6433705</v>
+        <v>6433704</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5084,7 +5090,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5103,10 +5108,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126202928</v>
+        <v>126193156</v>
       </c>
       <c r="B40" t="n">
-        <v>95604</v>
+        <v>58516</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5114,27 +5119,32 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2810</v>
+        <v>208249</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5142,10 +5152,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>338449</v>
+        <v>338453</v>
       </c>
       <c r="R40" t="n">
-        <v>6433705</v>
+        <v>6433720</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5189,6 +5199,16 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5205,10 +5225,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126280433</v>
+        <v>126203036</v>
       </c>
       <c r="B41" t="n">
-        <v>95964</v>
+        <v>95604</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5216,28 +5236,24 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -5248,10 +5264,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>338406</v>
+        <v>338481</v>
       </c>
       <c r="R41" t="n">
-        <v>6433747</v>
+        <v>6433705</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5278,12 +5294,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5311,10 +5327,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126280430</v>
+        <v>126202928</v>
       </c>
       <c r="B42" t="n">
-        <v>95964</v>
+        <v>95604</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5322,28 +5338,24 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -5354,10 +5366,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>338322</v>
+        <v>338449</v>
       </c>
       <c r="R42" t="n">
-        <v>6433729</v>
+        <v>6433705</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5384,12 +5396,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5417,32 +5429,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126391656</v>
+        <v>126280433</v>
       </c>
       <c r="B43" t="n">
-        <v>58300</v>
+        <v>95964</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103042</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5450,13 +5462,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5464,10 +5472,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>337674</v>
+        <v>338406</v>
       </c>
       <c r="R43" t="n">
-        <v>6433658</v>
+        <v>6433747</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5494,12 +5502,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5508,6 +5516,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5526,7 +5535,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126398365</v>
+        <v>126280430</v>
       </c>
       <c r="B44" t="n">
         <v>95964</v>
@@ -5569,10 +5578,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>338008</v>
+        <v>338322</v>
       </c>
       <c r="R44" t="n">
-        <v>6433676</v>
+        <v>6433729</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5599,17 +5608,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ca 45 - 50 cm hög i äldre skog</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5637,42 +5641,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126398382</v>
+        <v>126391656</v>
       </c>
       <c r="B45" t="n">
-        <v>95964</v>
+        <v>58300</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>103042</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5680,10 +5688,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>338036</v>
+        <v>337674</v>
       </c>
       <c r="R45" t="n">
-        <v>6433654</v>
+        <v>6433658</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5710,12 +5718,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5724,7 +5732,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5743,7 +5750,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126398378</v>
+        <v>126398365</v>
       </c>
       <c r="B46" t="n">
         <v>95964</v>
@@ -5786,10 +5793,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>337846</v>
+        <v>338008</v>
       </c>
       <c r="R46" t="n">
-        <v>6433661</v>
+        <v>6433676</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5854,7 +5861,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126398359</v>
+        <v>126398382</v>
       </c>
       <c r="B47" t="n">
         <v>95964</v>
@@ -5884,7 +5891,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5897,10 +5904,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>338012</v>
+        <v>338036</v>
       </c>
       <c r="R47" t="n">
-        <v>6433665</v>
+        <v>6433654</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5933,11 +5940,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ca 45 - 50 cm hög i äldre skog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5965,7 +5967,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126398385</v>
+        <v>126398378</v>
       </c>
       <c r="B48" t="n">
         <v>95964</v>
@@ -5995,7 +5997,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -6008,7 +6010,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>338031</v>
+        <v>337846</v>
       </c>
       <c r="R48" t="n">
         <v>6433661</v>
@@ -6044,6 +6046,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ca 45 - 50 cm hög i äldre skog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6071,7 +6078,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126398373</v>
+        <v>126398359</v>
       </c>
       <c r="B49" t="n">
         <v>95964</v>
@@ -6099,7 +6106,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -6110,10 +6121,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>337826</v>
+        <v>338012</v>
       </c>
       <c r="R49" t="n">
-        <v>6433635</v>
+        <v>6433665</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6150,7 +6161,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Blåmossa växer ihop och täcker en större yta ca 3 x 2 m</t>
+          <t>Ca 45 - 50 cm hög i äldre skog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6178,10 +6189,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126475340</v>
+        <v>126398385</v>
       </c>
       <c r="B50" t="n">
-        <v>97231</v>
+        <v>95964</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6189,21 +6200,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>224361</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6212,11 +6223,7 @@
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -6225,10 +6232,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>338007</v>
+        <v>338031</v>
       </c>
       <c r="R50" t="n">
-        <v>6433672</v>
+        <v>6433661</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6255,17 +6262,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På hällmark i äldre tall / barrblandskog</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6278,16 +6280,7 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>Stig Ingvarsson</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
           <t>Grimhild Angertuva</t>
@@ -6302,10 +6295,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126475328</v>
+        <v>126398373</v>
       </c>
       <c r="B51" t="n">
-        <v>97231</v>
+        <v>95964</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6313,28 +6306,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>224361</v>
+        <v>2180</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -6345,10 +6334,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>338009</v>
+        <v>337826</v>
       </c>
       <c r="R51" t="n">
-        <v>6433681</v>
+        <v>6433635</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6375,12 +6364,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Blåmossa växer ihop och täcker en större yta ca 3 x 2 m</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6408,42 +6402,46 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126476117</v>
+        <v>126475340</v>
       </c>
       <c r="B52" t="n">
-        <v>57654</v>
+        <v>97231</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>224361</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6451,10 +6449,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>338031</v>
+        <v>338007</v>
       </c>
       <c r="R52" t="n">
-        <v>6433671</v>
+        <v>6433672</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6481,17 +6479,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska hack i barrlåga</t>
+          <t>På hällmark i äldre tall / barrblandskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6500,10 +6498,20 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AT52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW52" t="inlineStr">
         <is>
           <t>Grimhild Angertuva</t>
@@ -6518,10 +6526,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126476075</v>
+        <v>126475328</v>
       </c>
       <c r="B53" t="n">
-        <v>58516</v>
+        <v>97231</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6529,36 +6537,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>208249</v>
+        <v>224361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6566,10 +6569,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>337974</v>
+        <v>338009</v>
       </c>
       <c r="R53" t="n">
-        <v>6433674</v>
+        <v>6433681</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6596,12 +6599,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6629,7 +6632,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126475807</v>
+        <v>126476117</v>
       </c>
       <c r="B54" t="n">
         <v>57654</v>
@@ -6672,10 +6675,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>337732</v>
+        <v>338031</v>
       </c>
       <c r="R54" t="n">
-        <v>6433633</v>
+        <v>6433671</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6702,17 +6705,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska hackspår i barrlåga</t>
+          <t>Färska hack i barrlåga</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6739,10 +6742,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126475899</v>
+        <v>126476075</v>
       </c>
       <c r="B55" t="n">
-        <v>58027</v>
+        <v>58516</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6750,21 +6753,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>208249</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6772,17 +6775,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6790,13 +6790,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>338013</v>
+        <v>337974</v>
       </c>
       <c r="R55" t="n">
-        <v>6433667</v>
+        <v>6433674</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6820,12 +6820,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6834,6 +6834,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6852,10 +6853,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129357810</v>
+        <v>126475807</v>
       </c>
       <c r="B56" t="n">
-        <v>56602</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6863,51 +6864,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>205998</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår Sopekärr , Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>338168</v>
+        <v>337732</v>
       </c>
       <c r="R56" t="n">
-        <v>6433691</v>
+        <v>6433633</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6934,27 +6926,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>20:30</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>20:30</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Flertalet ljudupptagningar i sumpskog med kärräng. Hålträn finns i området, upplever området som en passande miljö för arten.</t>
+          <t>Färska hackspår i barrlåga</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6966,26 +6948,7 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Sumpskog med kärräng, blandskog</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>Emily Macgregor</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
           <t>Grimhild Angertuva</t>
@@ -7000,32 +6963,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129529866</v>
+        <v>126475899</v>
       </c>
       <c r="B57" t="n">
-        <v>56602</v>
+        <v>58027</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>205998</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7033,32 +6996,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>338096</v>
+        <v>338013</v>
       </c>
       <c r="R57" t="n">
-        <v>6433664</v>
+        <v>6433667</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7082,22 +7044,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7109,16 +7061,7 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>Emily Macgregor</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
           <t>Grimhild Angertuva</t>
@@ -7133,10 +7076,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129914481</v>
+        <v>129357810</v>
       </c>
       <c r="B58" t="n">
-        <v>56691</v>
+        <v>56602</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7163,7 +7106,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -7181,103 +7124,384 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mickelsdamm Sopekärr , Vg</t>
+          <t>Mickelsdamm Skår Sopekärr , Vg</t>
         </is>
       </c>
       <c r="Q58" t="n">
         <v>338168</v>
       </c>
       <c r="R58" t="n">
+        <v>6433691</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Flertalet ljudupptagningar i sumpskog med kärräng. Hålträn finns i området, upplever området som en passande miljö för arten.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Sumpskog med kärräng, blandskog</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129529866</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56602</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>338096</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6433664</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129914481</v>
+      </c>
+      <c r="B60" t="n">
+        <v>56691</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Sopekärr , Vg</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>338168</v>
+      </c>
+      <c r="R60" t="n">
         <v>6433692</v>
       </c>
-      <c r="S58" t="n">
+      <c r="S60" t="n">
         <v>10</v>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>Västra Götaland</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>Ale</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>Västergötland</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>Skepplanda</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>22:13</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>22:13</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>28-30 kHz</t>
         </is>
       </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
         <is>
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AI58" t="inlineStr">
+      <c r="AI60" t="inlineStr">
         <is>
           <t>Naturskog, kuperad blandskog med våtmark och öppna luckor</t>
         </is>
       </c>
-      <c r="AS58" t="inlineStr">
+      <c r="AS60" t="inlineStr">
         <is>
           <t>Emily Macgregor</t>
         </is>
       </c>
-      <c r="AT58" t="inlineStr">
+      <c r="AT60" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="AW58" t="inlineStr">
+      <c r="AW60" t="inlineStr">
         <is>
           <t>Grimhild Angertuva</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
+      <c r="AX60" t="inlineStr">
         <is>
           <t>Grimhild Angertuva</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
